--- a/M-Priour-patch-1/ig/StructureDefinition-tddui-organization.xlsx
+++ b/M-Priour-patch-1/ig/StructureDefinition-tddui-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T14:04:26+00:00</t>
+    <t>2026-06-16T14:25:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/M-Priour-patch-1/ig/StructureDefinition-tddui-organization.xlsx
+++ b/M-Priour-patch-1/ig/StructureDefinition-tddui-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T14:25:35+00:00</t>
+    <t>2026-06-16T15:50:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
